--- a/docs/reports/內在價值報告_20260922.xlsx
+++ b/docs/reports/內在價值報告_20260922.xlsx
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>508.34</v>
+        <v>503.515</v>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="AE11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>268.515</v>
+        <v>269.136</v>
       </c>
       <c r="E24" s="8" t="inlineStr"/>
       <c r="F24" s="7" t="inlineStr">
@@ -3494,22 +3494,22 @@
       </c>
       <c r="H24" s="8" t="inlineStr"/>
       <c r="I24" s="9" t="n">
-        <v>480.806</v>
+        <v>480.8055</v>
       </c>
       <c r="J24" s="9" t="n">
         <v>9.3416</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>17.7685</v>
+        <v>17.7683</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>-44.2</v>
+        <v>-44</v>
       </c>
       <c r="M24" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>360.6045</v>
+        <v>360.6041</v>
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AE24" s="7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AF24" s="8" t="inlineStr">
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="D48" s="24" t="n">
-        <v>334.815</v>
+        <v>343.045</v>
       </c>
       <c r="E48" s="23" t="inlineStr"/>
       <c r="F48" s="22" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="H48" s="23" t="inlineStr"/>
       <c r="I48" s="24" t="n">
-        <v>49.1605</v>
+        <v>49.1602</v>
       </c>
       <c r="J48" s="24" t="n">
         <v>9.446</v>
@@ -6405,13 +6405,13 @@
         <v>34.7808</v>
       </c>
       <c r="L48" s="25" t="n">
-        <v>581.1</v>
+        <v>597.8</v>
       </c>
       <c r="M48" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N48" s="24" t="n">
-        <v>36.8704</v>
+        <v>36.8702</v>
       </c>
       <c r="O48" s="22" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="AE48" s="22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AF48" s="23" t="inlineStr">
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="D50" s="24" t="n">
-        <v>493.811</v>
+        <v>495.83</v>
       </c>
       <c r="E50" s="23" t="inlineStr"/>
       <c r="F50" s="22" t="inlineStr">
@@ -6647,7 +6647,7 @@
         <v>86.59699999999999</v>
       </c>
       <c r="L50" s="25" t="n">
-        <v>504.6</v>
+        <v>507.1</v>
       </c>
       <c r="M50" s="25" t="n">
         <v>25</v>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="AE50" s="22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AF50" s="23" t="inlineStr">
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="D56" s="24" t="n">
-        <v>350.165</v>
+        <v>358.794</v>
       </c>
       <c r="E56" s="23" t="inlineStr"/>
       <c r="F56" s="22" t="inlineStr">
@@ -7369,13 +7369,13 @@
         <v>62.856</v>
       </c>
       <c r="J56" s="24" t="n">
-        <v>2.0171</v>
+        <v>2.017</v>
       </c>
       <c r="K56" s="24" t="n">
         <v>15.3128</v>
       </c>
       <c r="L56" s="25" t="n">
-        <v>457.1</v>
+        <v>470.8</v>
       </c>
       <c r="M56" s="25" t="n">
         <v>25</v>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="AE56" s="22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AF56" s="23" t="inlineStr">
@@ -12238,10 +12238,10 @@
         </is>
       </c>
       <c r="C52" s="34" t="n">
-        <v>334.815</v>
+        <v>343.045</v>
       </c>
       <c r="D52" s="34" t="n">
-        <v>49.1605</v>
+        <v>49.1602</v>
       </c>
       <c r="E52" s="34" t="n">
         <v>9.446</v>
@@ -12252,7 +12252,7 @@
       <c r="G52" s="34" t="inlineStr"/>
       <c r="H52" s="34" t="inlineStr"/>
       <c r="I52" s="34" t="n">
-        <v>8.8994</v>
+        <v>8.8986</v>
       </c>
       <c r="J52" s="34" t="n">
         <v>12.4164</v>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="C54" s="34" t="n">
-        <v>508.34</v>
+        <v>503.515</v>
       </c>
       <c r="D54" s="34" t="n">
         <v>1600617.8442</v>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="L54" s="34" t="inlineStr"/>
       <c r="M54" s="34" t="n">
-        <v>7.32</v>
+        <v>7.31</v>
       </c>
       <c r="N54" s="34" t="n">
         <v>8.800000000000001</v>
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="C57" s="34" t="n">
-        <v>350.165</v>
+        <v>358.794</v>
       </c>
       <c r="D57" s="34" t="n">
         <v>62.856</v>
@@ -12519,7 +12519,7 @@
       </c>
       <c r="H57" s="34" t="inlineStr"/>
       <c r="I57" s="34" t="n">
-        <v>2.0171</v>
+        <v>2.017</v>
       </c>
       <c r="J57" s="34" t="n">
         <v>3.797</v>
@@ -12560,10 +12560,10 @@
         </is>
       </c>
       <c r="C58" s="34" t="n">
-        <v>268.515</v>
+        <v>269.136</v>
       </c>
       <c r="D58" s="34" t="n">
-        <v>480.806</v>
+        <v>480.8055</v>
       </c>
       <c r="E58" s="34" t="n">
         <v>9.3416</v>
@@ -12574,10 +12574,10 @@
       <c r="G58" s="34" t="inlineStr"/>
       <c r="H58" s="34" t="inlineStr"/>
       <c r="I58" s="34" t="n">
-        <v>15.4533</v>
+        <v>15.4517</v>
       </c>
       <c r="J58" s="34" t="n">
-        <v>17.7685</v>
+        <v>17.7683</v>
       </c>
       <c r="K58" s="34" t="n">
         <v>6466.5299</v>
@@ -12723,7 +12723,7 @@
         </is>
       </c>
       <c r="C61" s="34" t="n">
-        <v>493.811</v>
+        <v>495.83</v>
       </c>
       <c r="D61" s="34" t="n">
         <v>81.6729</v>
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="C52" s="24" t="n">
-        <v>334.815</v>
+        <v>343.045</v>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
@@ -15654,19 +15654,19 @@
         </is>
       </c>
       <c r="E52" s="24" t="n">
-        <v>24.5802</v>
+        <v>24.5801</v>
       </c>
       <c r="F52" s="24" t="n">
-        <v>36.8704</v>
+        <v>36.8702</v>
       </c>
       <c r="G52" s="24" t="n">
-        <v>56.5345</v>
+        <v>56.5342</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>73.7407</v>
+        <v>73.7403</v>
       </c>
       <c r="I52" s="24" t="n">
-        <v>73.7407</v>
+        <v>73.7403</v>
       </c>
       <c r="J52" s="26" t="inlineStr">
         <is>
@@ -15674,10 +15674,10 @@
         </is>
       </c>
       <c r="K52" s="24" t="n">
-        <v>6.8107</v>
+        <v>6.9781</v>
       </c>
       <c r="L52" s="24" t="n">
-        <v>36.8704</v>
+        <v>36.8702</v>
       </c>
     </row>
     <row r="53">
@@ -15738,7 +15738,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>508.34</v>
+        <v>503.515</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         </is>
       </c>
       <c r="C57" s="24" t="n">
-        <v>350.165</v>
+        <v>358.794</v>
       </c>
       <c r="D57" s="22" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="K57" s="24" t="n">
-        <v>5.5709</v>
+        <v>5.7082</v>
       </c>
       <c r="L57" s="24" t="n">
         <v>47.142</v>
@@ -15922,7 +15922,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>268.515</v>
+        <v>269.136</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
@@ -15930,19 +15930,19 @@
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>240.403</v>
+        <v>240.4027</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>360.6045</v>
+        <v>360.6041</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>552.9269</v>
+        <v>552.9263</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>721.2089999999999</v>
+        <v>721.2082</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>721.2089999999999</v>
+        <v>721.2082</v>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
@@ -15950,10 +15950,10 @@
         </is>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.5585</v>
+        <v>0.5598</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>360.6045</v>
+        <v>360.6041</v>
       </c>
     </row>
     <row r="59">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="C61" s="24" t="n">
-        <v>493.811</v>
+        <v>495.83</v>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         </is>
       </c>
       <c r="K61" s="24" t="n">
-        <v>6.0462</v>
+        <v>6.0709</v>
       </c>
       <c r="L61" s="24" t="n">
         <v>61.2547</v>
@@ -21461,7 +21461,7 @@
         </is>
       </c>
       <c r="C52" s="34" t="n">
-        <v>334.815</v>
+        <v>343.045</v>
       </c>
       <c r="D52" s="32" t="n">
         <v>152198000000</v>
@@ -21635,7 +21635,7 @@
         </is>
       </c>
       <c r="C54" s="34" t="n">
-        <v>508.34</v>
+        <v>503.515</v>
       </c>
       <c r="D54" s="32" t="inlineStr"/>
       <c r="E54" s="32" t="n">
@@ -21879,7 +21879,7 @@
         </is>
       </c>
       <c r="C57" s="34" t="n">
-        <v>350.165</v>
+        <v>358.794</v>
       </c>
       <c r="D57" s="32" t="n">
         <v>137196000000</v>
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="C58" s="34" t="n">
-        <v>268.515</v>
+        <v>269.136</v>
       </c>
       <c r="D58" s="32" t="n">
         <v>31538000000</v>
@@ -22225,7 +22225,7 @@
         </is>
       </c>
       <c r="C61" s="34" t="n">
-        <v>493.811</v>
+        <v>495.83</v>
       </c>
       <c r="D61" s="32" t="n">
         <v>90007000000</v>
@@ -26240,7 +26240,7 @@
         </is>
       </c>
       <c r="C52" s="24" t="n">
-        <v>334.815</v>
+        <v>343.045</v>
       </c>
       <c r="D52" s="22" t="n">
         <v>3</v>
@@ -26362,7 +26362,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>508.34</v>
+        <v>503.515</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>5.5</v>
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="C57" s="24" t="n">
-        <v>350.165</v>
+        <v>358.794</v>
       </c>
       <c r="D57" s="22" t="n">
         <v>2.3</v>
@@ -26606,7 +26606,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>268.515</v>
+        <v>269.136</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>3.5</v>
@@ -26789,7 +26789,7 @@
         </is>
       </c>
       <c r="C61" s="24" t="n">
-        <v>493.811</v>
+        <v>495.83</v>
       </c>
       <c r="D61" s="22" t="n">
         <v>2.8</v>
